--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/WASHINGTON_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/WASHINGTON_2019.xlsx
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C230">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C703">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C704">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C745">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C749">
